--- a/data/macro/宏观数据_只读.xlsx
+++ b/data/macro/宏观数据_只读.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学高一下期末_班型" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学高一下期末_各班明细" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="深大AI录取数据" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="院校层次" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,390 +191,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,7 +477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5584,12 +5201,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5663,12 +5279,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6010,12 +5625,11 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6324,12 +5938,11 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6822,12 +6435,11 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6982,12 +6594,11 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9083,12 +8694,11 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9268,6 +8878,203 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>范围</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>梯队</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>预估总分门槛</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>预估总分上限</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>代表院校</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C9/顶尖985</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D2" t="n">
+        <v>750</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>清华,北大,复旦,上海交大,浙大</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>中坚985</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" t="n">
+        <v>669</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>南大,中科大,武大,华中科大,西安交大</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>普通985/顶尖211</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>630</v>
+      </c>
+      <c r="D4" t="n">
+        <v>649</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>东南,同济,北航,厦大,南开</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>中坚211</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>610</v>
+      </c>
+      <c r="D5" t="n">
+        <v>629</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>华东理工,南理工,苏大,暨大,西南财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>末流211/一本</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>592</v>
+      </c>
+      <c r="D6" t="n">
+        <v>609</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>宁波大学,浙工大,南邮,合工大,福大</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>二本/一段</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>492</v>
+      </c>
+      <c r="D7" t="n">
+        <v>591</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>浙理工,杭电,温大,浙工商,中计量</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>专科及以下</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>280</v>
+      </c>
+      <c r="D8" t="n">
+        <v>491</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/macro/宏观数据_只读.xlsx
+++ b/data/macro/宏观数据_只读.xlsx
@@ -10,12 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一分一段表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特控线" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赋分区间_浙江" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学25届单科对照" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学高一下期末_门槛" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学高一下期末_班型" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富阳中学高一下期末_各班明细" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="深大AI录取数据" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="院校层次" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="院校层次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校内划线_升级" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门槛数据" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单科对照" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本校对照表_总分" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,47 +32,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -81,42 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9DEE7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9DEE7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9DEE7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9DEE7"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5290,340 +5228,332 @@
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>浙江选考赋分区间（20等级）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>全省累计排名占比</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>对应赋分区间</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>前0%~3%</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>97~100</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>3%~6%</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>94~96</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>6%~10%</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>91~93</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>10%~15%</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>88~90</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>15%~21%</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>85~87</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>21%~28%</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>82~84</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>28%~36%</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>79~81</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>36%~43%</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>76~78</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>43%~50%</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>73~75</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>50%~57%</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>70~72</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>57%~64%</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>67~69</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>64%~71%</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>64~66</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>71%~78%</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>61~63</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>78%~84%</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>58~60</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>84%~89%</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>55~57</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>89%~93%</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>52~54</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>93%~96%</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>49~51</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>96%~98%</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>46~48</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>98%~99%</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>43~45</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>99%~100%</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>40~42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5634,309 +5564,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>富阳中学2025届高考各科名次-分数对照表</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>范围</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>梯队</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>预估总分门槛</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>预估总分上限</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>代表院校</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>学科</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>参考人数</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>第50名</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>第100名</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>第150名</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>第200名</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>第250名</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>第300名</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C9/顶尖985</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D2" t="n">
+        <v>750</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>清华,北大,复旦,上海交大,浙大</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>499</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>中坚985</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" t="n">
+        <v>669</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>南大,中科大,武大,华中科大,西安交大</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>499</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>普通985/顶尖211</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>630</v>
+      </c>
+      <c r="D4" t="n">
+        <v>649</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>东南,同济,北航,厦大,南开</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>生物</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>中坚211</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>610</v>
+      </c>
+      <c r="D5" t="n">
+        <v>629</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>华东理工,南理工,苏大,暨大,西南财经</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>历史</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>305</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>末流211/一本</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>592</v>
+      </c>
+      <c r="D6" t="n">
+        <v>609</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>宁波大学,浙工大,南邮,合工大,福大</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>地理</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>468</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>二本/一段</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>492</v>
+      </c>
+      <c r="D7" t="n">
+        <v>591</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>浙理工,杭电,温大,浙工商,中计量</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>政治</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>321</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>技术</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>前6名97-98分；90分以上16人；85分以上19人</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>专科及以下</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>280</v>
+      </c>
+      <c r="D8" t="n">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5947,493 +5761,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>富阳中学高一下期末·总人数门槛大盘（2027届/2028届）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>【上特控线】分段人数</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2027届划线</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>2027届上线</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2028届划线</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2028届上线</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>语数英综合</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>311.5</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>660</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>286.5</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>497</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>607</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>592</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>535</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>496</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>生物</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>政治</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>历史</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>地理</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>【上浙大线】分段人数</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2027届划线</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2027届上线</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2028届划线</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>2028届上线</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>语数英综合</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>367.5</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>355.5</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>生物</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>政治</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>历史</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>地理</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>41</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2027划线</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2027上线</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2028划线</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2028上线</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6444,155 +5802,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>富阳中学班型结构</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>班型</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>考试参与情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1班、2班</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>科创班（提前招生，初三下入学）</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>部分参加（1班和2班参加的部分不相同）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>3班、4班</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>理科实验班</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>全部正常参加</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>5-11班</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>普通班（理科方向）</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>正常参加</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12班</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>文科实验班</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>正常参加</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>13-16班</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>普通班（文科方向）</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>正常参加</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>全校总人数</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>835</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>16个班</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>用户所在班</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>8班（普通班/平行班，理科方向，53人）</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>考试名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>特控线分数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>特控线上线人数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>浙大线分数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>浙大线上线人数</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6603,2096 +5843,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>富阳中学高一下期末·各班各科明细（2028届）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>均分</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>浙大线人数</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>特控线人数</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>班级人数</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>相对进退</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>108.3</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>3班</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>4班</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>5班</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>6班</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>7班</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>96.87</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>-3.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>8班</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>9班</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>10班</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>11班</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>12班</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>13班</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>14班</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>102.1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>15班</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>语文</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>16班</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>-1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>3班</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>4班</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>116.3</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>5班</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>-4.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>6班</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>7班</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>101.2</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>8班</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>9班</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>-5.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>10班</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>11班</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>-2.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>12班</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>13班</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>-4.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>14班</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>15班</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>16班</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>3班</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>4班</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>5班</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>92.15000000000001</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>6班</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>97.93000000000001</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>7班</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>96.55</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>8班</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>9班</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>93.56</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>10班</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>94.43000000000001</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>11班</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>12班</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>13班</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>93.55</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>14班</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>15班</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>96.45</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>16班</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>95.39</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>3班</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>4班</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>5班</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>-2.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>6班</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>7班</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>8班</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>9班</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>-1.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>10班</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>11班</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>3班</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>4班</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>5班</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>6班</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>-3.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>7班</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>8班</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>9班</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>10班</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>-5.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>化学</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>11班</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>0.2%</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>校内排名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>高考等效分</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8703,376 +5874,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>深圳大学 人工智能 浙江省录取数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>专业名称</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>录取分</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>位次</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>未投放人工智能</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>最相近：软件工程(腾班)657分/9476位次，计算机科学与技术656分/9771位次</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>人工智能(腾班)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>658</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>9073</v>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>人工智能</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>652</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>10305</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>人工智能(IEEE荣誉班)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>653</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>9815</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>待提供</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>约7月23-24日出，用户表示会提供</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>待提供</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>明年提供</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>范围</t>
+          <t>校内排名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>梯队</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>预估总分门槛</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>预估总分上限</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>代表院校</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C9/顶尖985</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>670</v>
-      </c>
-      <c r="D2" t="n">
-        <v>750</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>清华,北大,复旦,上海交大,浙大</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>中坚985</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>650</v>
-      </c>
-      <c r="D3" t="n">
-        <v>669</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>南大,中科大,武大,华中科大,西安交大</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>普通985/顶尖211</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>630</v>
-      </c>
-      <c r="D4" t="n">
-        <v>649</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>东南,同济,北航,厦大,南开</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>中坚211</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>610</v>
-      </c>
-      <c r="D5" t="n">
-        <v>629</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>华东理工,南理工,苏大,暨大,西南财经</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>末流211/一本</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>592</v>
-      </c>
-      <c r="D6" t="n">
-        <v>609</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>宁波大学,浙工大,南邮,合工大,福大</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>二本/一段</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>492</v>
-      </c>
-      <c r="D7" t="n">
-        <v>591</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>浙理工,杭电,温大,浙工商,中计量</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>专科及以下</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>280</v>
-      </c>
-      <c r="D8" t="n">
-        <v>491</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>高考总分</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/macro/宏观数据_只读.xlsx
+++ b/data/macro/宏观数据_只读.xlsx
@@ -5148,7 +5148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5213,6 +5213,20 @@
       </c>
       <c r="D4" t="n">
         <v>268</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="n">
+        <v>594</v>
+      </c>
+      <c r="C5" t="n">
+        <v>494</v>
+      </c>
+      <c r="D5" t="n">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -5606,7 +5620,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D2" t="n">
         <v>750</v>
@@ -5632,7 +5646,7 @@
         <v>650</v>
       </c>
       <c r="D3" t="n">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5698,7 +5712,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D6" t="n">
         <v>609</v>
@@ -5721,10 +5735,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5744,10 +5758,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/宏观数据_只读.xlsx
+++ b/data/macro/宏观数据_只读.xlsx
@@ -5775,7 +5775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5804,6 +5804,110 @@
           <t>2028上线</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>特控分段</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>语数英综合</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>270</v>
+      </c>
+      <c r="E3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>浙大分段</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>语数英综合</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
